--- a/stories/arbres/ATOM-DIF.COR.001-03.xlsx
+++ b/stories/arbres/ATOM-DIF.COR.001-03.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -602,7 +602,6 @@
           <t>secondary_lessons</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -819,6 +818,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -833,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV6"/>
+  <dimension ref="A1:AW6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1127,6 +1138,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1151,7 +1167,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Maman emmène Lila dans le jardin. Tom arrive. Tom est plus grand. Lila est plus petite. Ils ont des tailles différentes. Un panier de pommes est posé. Lila hésite. Elle se dit que Tom atteint plus haut. Maman s'accroupit. Maman dit : les tailles différentes n'empêchent pas le jeu. On invite. On joue ensemble. Lila va vers Tom. Elle dit : tu veux le panier avec moi. Tom dit : oui. Tom tend une pomme tout près. Lila la pose. Ils font un tas. Parfois Tom pose plus haut. Parfois Lila pose tout bas. Les deux façons marchent. Plus tard, ils rentrent au salon. Maman sort des cerceaux. Tom enfile le grand. Lila enfile le petit. Lila se souvient. Elle invite. Tom dit oui. Ils font rouler les cerceaux. Maman dit : au jardin, puis ici. C'est la même leçon. Petit ou grand, on invite. On joue ensemble. Lila et Tom tapent dans leurs mains. Les tailles différentes sont encore là. Le jeu aussi.</t>
+          <t>Maman emmène Lila dans le jardin. Tom arrive. Tom est plus grand. Lila est plus petite. Ils ont des tailles différentes. Un panier de pommes est posé. Lila hésite. Elle se dit que Tom atteint plus haut. Maman s'accroupit. Les tailles différentes n'empêchent pas le jeu. On invite. On joue ensemble. Lila va vers Tom. Tu veux le panier avec moi. Oui. Tom tend une pomme tout près. Lila la pose. Ils font un tas. Parfois Tom pose plus haut. Parfois Lila pose tout bas. Les deux façons marchent. Plus tard, ils rentrent au salon. Maman sort des cerceaux. Tom enfile le grand. Lila enfile le petit. Lila se souvient. Elle invite. Tom dit oui. Ils font rouler les cerceaux. Au jardin, puis ici. C'est la même leçon. Petit ou grand, on invite. On joue ensemble. Lila et Tom tapent dans leurs mains. Les tailles différentes sont encore là. Le jeu aussi.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1289,6 +1305,18 @@
         <v>8</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|Maman emmène Lila dans le jardin. Tom arrive. Tom est plus grand. Lila est plus petite. Ils ont des tailles différentes. Un panier de pommes est posé. Lila hésite. Elle se dit que Tom atteint plus haut. Maman s'accroupit.
+maman|Les tailles différentes n'empêchent pas le jeu. On invite. On joue ensemble.
+narrateur|Lila va vers Tom.
+narrateur|Tu veux le panier avec moi.
+copain|Oui.
+narrateur|Tom tend une pomme tout près. Lila la pose. Ils font un tas. Parfois Tom pose plus haut. Parfois Lila pose tout bas. Les deux façons marchent. Plus tard, ils rentrent au salon. Maman sort des cerceaux. Tom enfile le grand. Lila enfile le petit. Lila se souvient. Elle invite. Tom dit oui. Ils font rouler les cerceaux.
+maman|Au jardin, puis ici. C'est la même leçon. Petit ou grand, on invite. On joue ensemble.
+narrateur|Lila et Tom tapent dans leurs mains. Les tailles différentes sont encore là. Le jeu aussi.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1465,6 +1493,11 @@
       <c r="AV3" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|Lila est plus petite. Tom est plus grand. Que font-ils ?</t>
         </is>
       </c>
     </row>
@@ -1633,6 +1666,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|Lila a invité. Tom a tendu la pomme tout près. Ils ont des tailles différentes. Ils ont joué ensemble.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1795,6 +1833,11 @@
         <v>8</v>
       </c>
       <c r="AV5" s="2" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|Maman range les cerceaux. Lila et Tom se disent à demain.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1957,6 +2000,11 @@
         <v>8</v>
       </c>
       <c r="AV6" s="2" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -1975,7 +2023,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -1992,6 +2040,13 @@
       <c r="A2" t="inlineStr">
         <is>
           <t>conversion structurelle, prompts de choix alignés, TTS profilé</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-DIF.COR.001-03.xlsx
+++ b/stories/arbres/ATOM-DIF.COR.001-03.xlsx
@@ -844,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW6"/>
+  <dimension ref="A1:AX6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1143,6 +1143,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1317,6 +1322,7 @@
 narrateur|Lila et Tom tapent dans leurs mains. Les tailles différentes sont encore là. Le jeu aussi.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1500,6 +1506,7 @@
           <t>narrateur|Lila est plus petite. Tom est plus grand. Que font-ils ?</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1671,6 +1678,7 @@
           <t>narrateur|Lila a invité. Tom a tendu la pomme tout près. Ils ont des tailles différentes. Ils ont joué ensemble.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1838,6 +1846,7 @@
           <t>narrateur|Maman range les cerceaux. Lila et Tom se disent à demain.</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -2005,6 +2014,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2023,7 +2033,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2047,6 +2057,20 @@
       <c r="A3" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -2061,7 +2085,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -2248,6 +2272,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/stories/arbres/ATOM-DIF.COR.001-03.xlsx
+++ b/stories/arbres/ATOM-DIF.COR.001-03.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B30"/>
+  <dimension ref="A1:B31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -544,7 +544,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Lila et Tom jouent ensemble</t>
+          <t>Nino et le panier de pommes</t>
         </is>
       </c>
     </row>
@@ -602,6 +602,11 @@
           <t>secondary_lessons</t>
         </is>
       </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>DIF.BES.002</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -830,6 +835,18 @@
       <c r="B30" t="inlineStr">
         <is>
           <t>voix-roles-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>fil_rouge</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Sous le pommier, Nino invite Mila à ranger les pommes. Ils ont des tailles différentes. Plus tard, au salon, ils font rouler les cerceaux, ensemble.</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1189,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Maman emmène Lila dans le jardin. Tom arrive. Tom est plus grand. Lila est plus petite. Ils ont des tailles différentes. Un panier de pommes est posé. Lila hésite. Elle se dit que Tom atteint plus haut. Maman s'accroupit. Les tailles différentes n'empêchent pas le jeu. On invite. On joue ensemble. Lila va vers Tom. Tu veux le panier avec moi. Oui. Tom tend une pomme tout près. Lila la pose. Ils font un tas. Parfois Tom pose plus haut. Parfois Lila pose tout bas. Les deux façons marchent. Plus tard, ils rentrent au salon. Maman sort des cerceaux. Tom enfile le grand. Lila enfile le petit. Lila se souvient. Elle invite. Tom dit oui. Ils font rouler les cerceaux. Au jardin, puis ici. C'est la même leçon. Petit ou grand, on invite. On joue ensemble. Lila et Tom tapent dans leurs mains. Les tailles différentes sont encore là. Le jeu aussi.</t>
+          <t>Sous le pommier, un panier d'osier attend. Une feuille est collée sur une pomme. La lumière passe entre les branches. Ça sent le fruit mûr, un peu sucré. L'herbe est tiède sous les pieds. Maman pose le panier tout bas. En ce moment, Nino regarde les pommes. Maman, elles roulent ! Oui, Nino. On les met dans le panier ? Oui. Mila arrive sous l'arbre. Mila est plus petite. Nino est plus grand. Ils ont des tailles différentes. Nino hésite un peu. Les tailles différentes n'empêchent pas le jeu. On invite. On joue ensemble. Nino va vers Mila. Tu veux le panier avec moi ? Oui. Mila tend une pomme tout près. Nino la pose dans l'osier. Parfois Nino pose plus haut. Parfois Mila pose tout bas. Les deux façons marchent. Vous jouez ensemble. Bravo.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1312,14 +1329,35 @@
       <c r="AV2" s="2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>narrateur|Maman emmène Lila dans le jardin. Tom arrive. Tom est plus grand. Lila est plus petite. Ils ont des tailles différentes. Un panier de pommes est posé. Lila hésite. Elle se dit que Tom atteint plus haut. Maman s'accroupit.
-maman|Les tailles différentes n'empêchent pas le jeu. On invite. On joue ensemble.
-narrateur|Lila va vers Tom.
-narrateur|Tu veux le panier avec moi.
-copain|Oui.
-narrateur|Tom tend une pomme tout près. Lila la pose. Ils font un tas. Parfois Tom pose plus haut. Parfois Lila pose tout bas. Les deux façons marchent. Plus tard, ils rentrent au salon. Maman sort des cerceaux. Tom enfile le grand. Lila enfile le petit. Lila se souvient. Elle invite. Tom dit oui. Ils font rouler les cerceaux.
-maman|Au jardin, puis ici. C'est la même leçon. Petit ou grand, on invite. On joue ensemble.
-narrateur|Lila et Tom tapent dans leurs mains. Les tailles différentes sont encore là. Le jeu aussi.</t>
+          <t>narrateur|Sous le pommier, un panier d'osier attend.
+narrateur|Une feuille est collée sur une pomme.
+narrateur|La lumière passe entre les branches.
+narrateur|Ça sent le fruit mûr, un peu sucré.
+narrateur|L'herbe est tiède sous les pieds.
+narrateur|Maman pose le panier tout bas.
+narrateur|En ce moment, Nino regarde les pommes.
+enfant-m|Maman, elles roulent !
+maman|Oui, Nino.
+maman|On les met dans le panier ?
+enfant-m|Oui.
+narrateur|Mila arrive sous l'arbre.
+narrateur|Mila est plus petite.
+narrateur|Nino est plus grand.
+narrateur|Ils ont des tailles différentes.
+narrateur|Nino hésite un peu.
+maman|Les tailles différentes n'empêchent pas le jeu.
+maman|On invite.
+maman|On joue ensemble.
+narrateur|Nino va vers Mila.
+enfant-m|Tu veux le panier avec moi ?
+copine|Oui.
+narrateur|Mila tend une pomme tout près.
+narrateur|Nino la pose dans l'osier.
+narrateur|Parfois Nino pose plus haut.
+narrateur|Parfois Mila pose tout bas.
+narrateur|Les deux façons marchent.
+maman|Vous jouez ensemble.
+maman|Bravo.</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr"/>
@@ -1347,7 +1385,7 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Lila est plus petite. Tom est plus grand. Que font-ils ?</t>
+          <t>Nino est plus grand. Mila est plus petite. Que font-ils ?</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
@@ -1503,7 +1541,9 @@
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>narrateur|Lila est plus petite. Tom est plus grand. Que font-ils ?</t>
+          <t>narrateur|Nino est plus grand.
+narrateur|Mila est plus petite.
+narrateur|Que font-ils ?</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr"/>
@@ -1531,7 +1571,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Lila a invité. Tom a tendu la pomme tout près. Ils ont des tailles différentes. Ils ont joué ensemble.</t>
+          <t>Plus tard, ils rentrent au salon. Le tapis sent encore le soleil. Maman sort des cerceaux. Nino prend le grand. Mila prend le petit. Nino se souvient. Tu veux rouler avec moi ? Oui. Ils font rouler les cerceaux. Le grand roule plus loin. Le petit reste près des pieds. Au jardin, puis ici. Petit ou grand, on invite. On joue ensemble. Bravo, Nino. Tu as fait du bon travail. Nino et Mila tapent dans leurs mains. Vous avez des tailles différentes. Et vous jouez ensemble. Le cerceau a bien roulé ? Oui, maman.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -1675,7 +1715,27 @@
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>narrateur|Lila a invité. Tom a tendu la pomme tout près. Ils ont des tailles différentes. Ils ont joué ensemble.</t>
+          <t>narrateur|Plus tard, ils rentrent au salon.
+narrateur|Le tapis sent encore le soleil.
+narrateur|Maman sort des cerceaux.
+narrateur|Nino prend le grand.
+narrateur|Mila prend le petit.
+narrateur|Nino se souvient.
+enfant-m|Tu veux rouler avec moi ?
+copine|Oui.
+narrateur|Ils font rouler les cerceaux.
+narrateur|Le grand roule plus loin.
+narrateur|Le petit reste près des pieds.
+maman|Au jardin, puis ici.
+maman|Petit ou grand, on invite.
+maman|On joue ensemble.
+maman|Bravo, Nino.
+maman|Tu as fait du bon travail.
+narrateur|Nino et Mila tapent dans leurs mains.
+maman|Vous avez des tailles différentes.
+maman|Et vous jouez ensemble.
+maman|Le cerceau a bien roulé ?
+enfant-m|Oui, maman.</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr"/>
@@ -1703,7 +1763,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Maman range les cerceaux. Lila et Tom se disent à demain.</t>
+          <t>On range les cerceaux ? Oui. Maman glisse les cerceaux sous le canapé. Nino pose le panier près de la porte. Une pomme brille encore. À demain. À demain. Bravo. Tu as invité. Vous avez joué ensemble. Le salon redevient calme.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -1843,7 +1903,17 @@
       <c r="AV5" s="2" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>narrateur|Maman range les cerceaux. Lila et Tom se disent à demain.</t>
+          <t>maman|On range les cerceaux ?
+enfant-m|Oui.
+narrateur|Maman glisse les cerceaux sous le canapé.
+narrateur|Nino pose le panier près de la porte.
+narrateur|Une pomme brille encore.
+copine|À demain.
+enfant-m|À demain.
+maman|Bravo.
+maman|Tu as invité.
+maman|Vous avez joué ensemble.
+narrateur|Le salon redevient calme.</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr"/>
@@ -1871,7 +1941,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>On a rangé les pommes. On a joué ensemble. Bravo. Tu as fait du bon travail. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -2011,7 +2081,11 @@
       <c r="AV6" s="2" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-m|On a rangé les pommes.
+enfant-m|On a joué ensemble.
+maman|Bravo.
+maman|Tu as fait du bon travail.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr"/>
@@ -2033,7 +2107,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2071,6 +2145,13 @@
       <c r="A5" t="inlineStr">
         <is>
           <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>F-NAR-009 ouverture du monde, fusion agents</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-DIF.COR.001-03.xlsx
+++ b/stories/arbres/ATOM-DIF.COR.001-03.xlsx
@@ -1189,7 +1189,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Sous le pommier, un panier d'osier attend. Une feuille est collée sur une pomme. La lumière passe entre les branches. Ça sent le fruit mûr, un peu sucré. L'herbe est tiède sous les pieds. Maman pose le panier tout bas. En ce moment, Nino regarde les pommes. Maman, elles roulent ! Oui, Nino. On les met dans le panier ? Oui. Mila arrive sous l'arbre. Mila est plus petite. Nino est plus grand. Ils ont des tailles différentes. Nino hésite un peu. Les tailles différentes n'empêchent pas le jeu. On invite. On joue ensemble. Nino va vers Mila. Tu veux le panier avec moi ? Oui. Mila tend une pomme tout près. Nino la pose dans l'osier. Parfois Nino pose plus haut. Parfois Mila pose tout bas. Les deux façons marchent. Vous jouez ensemble. Bravo.</t>
+          <t>Sous le pommier, un panier d'osier attend. Une feuille est collée sur une pomme. La lumière passe entre les branches. Ça sent le fruit mûr, un peu sucré. L'herbe est tiède sous les pieds. Maman pose le panier tout bas. En ce moment, Nino regarde les pommes. Maman, elles roulent ! Oui, Nino. On les met dans le panier ? Oui. Mila arrive sous l'arbre. Mila est plus petite. Nino est plus grand. Ils ont des tailles différentes. Nino hésite un peu. Les tailles différentes n'empêchent pas le jeu. On invite. On joue ensemble. Nino va vers Mila. Tu veux le panier avec moi ? Oui. Mila tend une pomme tout près. Nino la pose dans l'osier. Parfois Nino pose plus haut. Parfois Mila pose tout bas. Les deux façons marchent. Vous jouez ensemble. Bravo. Une pomme roule encore. Mila la rattrape tout bas. Nino ouvre le panier. Elle est collante ! Oui. C'est le sucre de la pomme. Vous continuez ensemble ? Oui.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1357,7 +1357,15 @@
 narrateur|Parfois Mila pose tout bas.
 narrateur|Les deux façons marchent.
 maman|Vous jouez ensemble.
-maman|Bravo.</t>
+maman|Bravo.
+narrateur|Une pomme roule encore.
+narrateur|Mila la rattrape tout bas.
+narrateur|Nino ouvre le panier.
+enfant-m|Elle est collante !
+maman|Oui.
+maman|C'est le sucre de la pomme.
+maman|Vous continuez ensemble ?
+enfant-m|Oui.</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr"/>
@@ -1571,7 +1579,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Plus tard, ils rentrent au salon. Le tapis sent encore le soleil. Maman sort des cerceaux. Nino prend le grand. Mila prend le petit. Nino se souvient. Tu veux rouler avec moi ? Oui. Ils font rouler les cerceaux. Le grand roule plus loin. Le petit reste près des pieds. Au jardin, puis ici. Petit ou grand, on invite. On joue ensemble. Bravo, Nino. Tu as fait du bon travail. Nino et Mila tapent dans leurs mains. Vous avez des tailles différentes. Et vous jouez ensemble. Le cerceau a bien roulé ? Oui, maman.</t>
+          <t>Plus tard, ils rentrent au salon. Le tapis sent encore le soleil. Maman sort des cerceaux. Nino prend le grand. Mila prend le petit. Nino se souvient. Tu veux rouler avec moi ? Oui. Ils font rouler les cerceaux. Le grand roule plus loin. Le petit reste près des pieds. Au jardin, puis ici. Petit ou grand, on invite. On joue ensemble. Bravo, Nino. Tu as fait du bon travail. Nino et Mila tapent dans leurs mains. Vous avez des tailles différentes. Et vous jouez ensemble. Le cerceau a bien roulé ? Oui, maman. Le petit cerceau s'arrête près du tapis. Mila le reprend, tout doux. Nino attend son tour. Tu as attendu, Nino. Bravo.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -1735,7 +1743,12 @@
 maman|Vous avez des tailles différentes.
 maman|Et vous jouez ensemble.
 maman|Le cerceau a bien roulé ?
-enfant-m|Oui, maman.</t>
+enfant-m|Oui, maman.
+narrateur|Le petit cerceau s'arrête près du tapis.
+narrateur|Mila le reprend, tout doux.
+narrateur|Nino attend son tour.
+maman|Tu as attendu, Nino.
+maman|Bravo.</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr"/>
@@ -1763,7 +1776,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>On range les cerceaux ? Oui. Maman glisse les cerceaux sous le canapé. Nino pose le panier près de la porte. Une pomme brille encore. À demain. À demain. Bravo. Tu as invité. Vous avez joué ensemble. Le salon redevient calme.</t>
+          <t>On range les cerceaux ? Oui. Maman glisse les cerceaux sous le canapé. Nino pose le panier près de la porte. Une pomme brille encore. Le salon sent le fruit et le tapis chaud. À demain. À demain. Bravo. Tu as invité. Vous avez joué ensemble. Le salon redevient calme.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -1908,6 +1921,7 @@
 narrateur|Maman glisse les cerceaux sous le canapé.
 narrateur|Nino pose le panier près de la porte.
 narrateur|Une pomme brille encore.
+narrateur|Le salon sent le fruit et le tapis chaud.
 copine|À demain.
 enfant-m|À demain.
 maman|Bravo.
@@ -2107,7 +2121,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A6"/>
+  <dimension ref="A1:A9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2150,6 +2164,27 @@
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
+        <is>
+          <t>F-NAR-009 ouverture du monde, fusion agents</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>F-NAR-009 ouverture du monde, fusion agents</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>F-NAR-009 ouverture du monde, fusion agents</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
         <is>
           <t>F-NAR-009 ouverture du monde, fusion agents</t>
         </is>

--- a/stories/arbres/ATOM-DIF.COR.001-03.xlsx
+++ b/stories/arbres/ATOM-DIF.COR.001-03.xlsx
@@ -544,7 +544,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Nino et le panier de pommes</t>
+          <t>Les bateaux de pomme</t>
         </is>
       </c>
     </row>
@@ -846,7 +846,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Sous le pommier, Nino invite Mila à ranger les pommes. Ils ont des tailles différentes. Plus tard, au salon, ils font rouler les cerceaux, ensemble.</t>
+          <t>Nino veut faire flotter des bateaux de pomme. La bassine est trop haute pour Mila. Ils la posent sur la marche et soufflent ensemble jusqu'au bord.</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Sous le pommier, un panier d'osier attend. Une feuille est collée sur une pomme. La lumière passe entre les branches. Ça sent le fruit mûr, un peu sucré. L'herbe est tiède sous les pieds. Maman pose le panier tout bas. En ce moment, Nino regarde les pommes. Maman, elles roulent ! Oui, Nino. On les met dans le panier ? Oui. Mila arrive sous l'arbre. Mila est plus petite. Nino est plus grand. Ils ont des tailles différentes. Nino hésite un peu. Les tailles différentes n'empêchent pas le jeu. On invite. On joue ensemble. Nino va vers Mila. Tu veux le panier avec moi ? Oui. Mila tend une pomme tout près. Nino la pose dans l'osier. Parfois Nino pose plus haut. Parfois Mila pose tout bas. Les deux façons marchent. Vous jouez ensemble. Bravo. Une pomme roule encore. Mila la rattrape tout bas. Nino ouvre le panier. Elle est collante ! Oui. C'est le sucre de la pomme. Vous continuez ensemble ? Oui.</t>
+          <t>La tarte aux pommes fume encore. Elle sent le beurre. Maman l'a posée sur la pierre. La pierre est froide, sous le plat. Une pomme tombée attend dans l'herbe. Une feuille y est collée. Tu as senti la tarte, Nino ? Oui, maman. Elle est chaude. Elle va refroidir. Je veux un bateau de pomme. Dans la bassine ? Oui. En ce moment, Nino prend la pomme. Elle est collante, un peu sucrée. Maman pose une bassine d'eau. La bassine est sur la table. Mila arrive sous l'arbre. Mila est plus petite. Nino est plus grand. Ils ont des tailles différentes. Tu veux le bateau avec moi ? Oui. Mila lève les mains. La table est trop haute pour elle. Elle n'atteint pas. On pose la bassine plus bas. Maman la pose sur la marche. L'eau tremble, puis s'arrête. Vous jouez ensemble, là. On peut jouer ensemble. Nino met une feuille en voile. Mila pousse la pomme dans l'eau. La pomme tourne, tout seule. Elle fait des ronds ! Oui. On souffle ? Oui. Ils soufflent ensemble. L'eau fait de toutes petites vagues. Ça sent encore le beurre, derrière. La tarte attend. Le bateau d'abord.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Maman emmène Lila dans le jardin. Tom arrive. Tom est plus grand. Lila est plus petite. Ils ont des &lt;emphasis level="moderate"&gt;tailles&lt;/emphasis&gt; différentes. Un panier de pommes est posé. Lila hésite. Elle se dit que Tom atteint plus haut. Maman s'accroupit. Maman dit : les tailles différentes n'empêchent pas le jeu. On invite. On joue ensemble. Lila va vers Tom. Elle dit : tu veux le panier avec moi. Tom dit : oui. Tom tend une pomme tout près. Lila la pose. Ils font un tas. Parfois Tom pose plus haut. Parfois Lila pose tout bas. Les deux façons marchent. Plus tard, ils rentrent au salon. Maman sort des cerceaux. Tom enfile le grand. Lila enfile le petit. Lila se souvient. Elle invite. Tom dit oui. Ils font rouler les cerceaux. Maman dit : au jardin, puis ici. C'est la même leçon. Petit ou grand, on invite. On joue ensemble. Lila et Tom tapent dans leurs mains. Les tailles différentes sont encore là. Le jeu aussi.&lt;/prosody&gt;&lt;break time="400ms"/&gt;&lt;/speak&gt;</t>
+          <t>La tarte aux pommes fume encore. Elle sent le beurre. Maman l'a posée sur la pierre. La pierre est froide, sous le plat. Une pomme tombée attend dans l'herbe. Une feuille y est collée. Tu as senti la tarte, Nino ? Oui, maman. Elle est chaude. Elle va refroidir. Je veux un bateau de pomme. Dans la bassine ? Oui. En ce moment, Nino prend la pomme. Elle est collante, un peu sucrée. Maman pose une bassine d'eau. La bassine est sur la table. Mila arrive sous l'arbre. Mila est plus petite. Nino est plus grand. Ils ont des tailles différentes. Tu veux le bateau avec moi ? Oui. Mila lève les mains. La table est trop haute pour elle. Elle n'atteint pas. On pose la bassine plus bas. Maman la pose sur la marche. L'eau tremble, puis s'arrête. Vous jouez ensemble, là. On peut jouer ensemble. Nino met une feuille en voile. Mila pousse la pomme dans l'eau. La pomme tourne, tout seule. Elle fait des ronds ! Oui. On souffle ? Oui. Ils soufflent ensemble. L'eau fait de toutes petites vagues. Ça sent encore le beurre, derrière. La tarte attend. Le bateau d'abord.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -1257,7 +1257,7 @@
         <v>0.96</v>
       </c>
       <c r="AB2" s="2" t="n">
-        <v>1.12</v>
+        <v>1.22</v>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
@@ -1329,46 +1329,51 @@
       <c r="AV2" s="2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>narrateur|Sous le pommier, un panier d'osier attend.
-narrateur|Une feuille est collée sur une pomme.
-narrateur|La lumière passe entre les branches.
-narrateur|Ça sent le fruit mûr, un peu sucré.
-narrateur|L'herbe est tiède sous les pieds.
-narrateur|Maman pose le panier tout bas.
-narrateur|En ce moment, Nino regarde les pommes.
-enfant-m|Maman, elles roulent !
-maman|Oui, Nino.
-maman|On les met dans le panier ?
+          <t>narrateur|La tarte aux pommes fume encore.
+narrateur|Elle sent le beurre.
+narrateur|Maman l'a posée sur la pierre.
+narrateur|La pierre est froide, sous le plat.
+narrateur|Une pomme tombée attend dans l'herbe.
+narrateur|Une feuille y est collée.
+maman|Tu as senti la tarte, Nino ?
+enfant-m|Oui, maman.
+enfant-m|Elle est chaude.
+maman|Elle va refroidir.
+enfant-m|Je veux un bateau de pomme.
+maman|Dans la bassine ?
 enfant-m|Oui.
+narrateur|En ce moment, Nino prend la pomme.
+narrateur|Elle est collante, un peu sucrée.
+narrateur|Maman pose une bassine d'eau.
+narrateur|La bassine est sur la table.
 narrateur|Mila arrive sous l'arbre.
 narrateur|Mila est plus petite.
 narrateur|Nino est plus grand.
 narrateur|Ils ont des tailles différentes.
-narrateur|Nino hésite un peu.
-maman|Les tailles différentes n'empêchent pas le jeu.
-maman|On invite.
-maman|On joue ensemble.
-narrateur|Nino va vers Mila.
-enfant-m|Tu veux le panier avec moi ?
+enfant-m|Tu veux le bateau avec moi ?
 copine|Oui.
-narrateur|Mila tend une pomme tout près.
-narrateur|Nino la pose dans l'osier.
-narrateur|Parfois Nino pose plus haut.
-narrateur|Parfois Mila pose tout bas.
-narrateur|Les deux façons marchent.
-maman|Vous jouez ensemble.
-maman|Bravo.
-narrateur|Une pomme roule encore.
-narrateur|Mila la rattrape tout bas.
-narrateur|Nino ouvre le panier.
-enfant-m|Elle est collante !
+narrateur|Mila lève les mains.
+narrateur|La table est trop haute pour elle.
+enfant-m|Elle n'atteint pas.
+maman|On pose la bassine plus bas.
+narrateur|Maman la pose sur la marche.
+narrateur|L'eau tremble, puis s'arrête.
+maman|Vous jouez ensemble, là.
+maman|On peut jouer ensemble.
+narrateur|Nino met une feuille en voile.
+narrateur|Mila pousse la pomme dans l'eau.
+narrateur|La pomme tourne, tout seule.
+enfant-m|Elle fait des ronds !
 maman|Oui.
-maman|C'est le sucre de la pomme.
-maman|Vous continuez ensemble ?
-enfant-m|Oui.</t>
-        </is>
-      </c>
-      <c r="AX2" t="inlineStr"/>
+copine|On souffle ?
+enfant-m|Oui.
+narrateur|Ils soufflent ensemble.
+narrateur|L'eau fait de toutes petites vagues.
+narrateur|Ça sent encore le beurre, derrière.
+maman|La tarte attend.
+enfant-m|Le bateau d'abord.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1398,7 +1403,7 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Lila est plus petite. Tom est plus grand. Que font-ils ?&lt;/prosody&gt;&lt;break time="250ms"/&gt;&lt;/speak&gt;</t>
+          <t>Nino est plus grand. Mila est plus petite. Que font-ils ?</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -1428,7 +1433,7 @@
       </c>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>Ils ont des tailles différentes. Que font Lila et Tom ?</t>
+          <t>Ils jouent ensemble. Que font Nino et Mila ?</t>
         </is>
       </c>
       <c r="M3" s="2" t="inlineStr"/>
@@ -1470,7 +1475,7 @@
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>slow</t>
         </is>
       </c>
       <c r="AA3" s="2" t="n">
@@ -1554,7 +1559,6 @@
 narrateur|Que font-ils ?</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1579,12 +1583,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Plus tard, ils rentrent au salon. Le tapis sent encore le soleil. Maman sort des cerceaux. Nino prend le grand. Mila prend le petit. Nino se souvient. Tu veux rouler avec moi ? Oui. Ils font rouler les cerceaux. Le grand roule plus loin. Le petit reste près des pieds. Au jardin, puis ici. Petit ou grand, on invite. On joue ensemble. Bravo, Nino. Tu as fait du bon travail. Nino et Mila tapent dans leurs mains. Vous avez des tailles différentes. Et vous jouez ensemble. Le cerceau a bien roulé ? Oui, maman. Le petit cerceau s'arrête près du tapis. Mila le reprend, tout doux. Nino attend son tour. Tu as attendu, Nino. Bravo.</t>
+          <t>Le bateau arrive au bord. Mila le rattrape tout bas. Nino en prépare un autre. Une feuille verte, une pomme jaune. Deux bateaux, maintenant. Oui. Les deux façons marchent. Parfois Nino pousse plus loin. Parfois Mila pousse tout près. Les pommes se croisent. La mienne a tourné ! La mienne aussi. Vous avez des tailles différentes. Et vous jouez ensemble. Le bateau a bien flotté ? Oui, maman. Une goutte tombe de la feuille. Elle fait un rond dans l'eau. La tarte ne fume plus. Elle sent encore le beurre. Elle est prête ? Presque. Un bateau encore, si vous voulez. Encore un.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Lila a invité. Tom a tendu la pomme tout près. Ils ont des &lt;emphasis level="moderate"&gt;tailles&lt;/emphasis&gt; différentes. Ils ont joué ensemble.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Le bateau arrive au bord. Mila le rattrape tout bas. Nino en prépare un autre. Une feuille verte, une pomme jaune. Deux bateaux, maintenant. Oui. Les deux façons marchent. Parfois Nino pousse plus loin. Parfois Mila pousse tout près. Les pommes se croisent. La mienne a tourné ! La mienne aussi. Vous avez des tailles différentes. Et vous jouez ensemble. Le bateau a bien flotté ? Oui, maman. Une goutte tombe de la feuille. Elle fait un rond dans l'eau. La tarte ne fume plus. Elle sent encore le beurre. Elle est prête ? Presque. Un bateau encore, si vous voulez. Encore un.</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -1647,7 +1651,7 @@
         <v>0.96</v>
       </c>
       <c r="AB4" s="2" t="n">
-        <v>1.12</v>
+        <v>1.22</v>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
@@ -1723,35 +1727,32 @@
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>narrateur|Plus tard, ils rentrent au salon.
-narrateur|Le tapis sent encore le soleil.
-narrateur|Maman sort des cerceaux.
-narrateur|Nino prend le grand.
-narrateur|Mila prend le petit.
-narrateur|Nino se souvient.
-enfant-m|Tu veux rouler avec moi ?
-copine|Oui.
-narrateur|Ils font rouler les cerceaux.
-narrateur|Le grand roule plus loin.
-narrateur|Le petit reste près des pieds.
-maman|Au jardin, puis ici.
-maman|Petit ou grand, on invite.
-maman|On joue ensemble.
-maman|Bravo, Nino.
-maman|Tu as fait du bon travail.
-narrateur|Nino et Mila tapent dans leurs mains.
+          <t>narrateur|Le bateau arrive au bord.
+narrateur|Mila le rattrape tout bas.
+narrateur|Nino en prépare un autre.
+narrateur|Une feuille verte, une pomme jaune.
+enfant-m|Deux bateaux, maintenant.
+maman|Oui.
+maman|Les deux façons marchent.
+narrateur|Parfois Nino pousse plus loin.
+narrateur|Parfois Mila pousse tout près.
+narrateur|Les pommes se croisent.
+copine|La mienne a tourné !
+enfant-m|La mienne aussi.
 maman|Vous avez des tailles différentes.
 maman|Et vous jouez ensemble.
-maman|Le cerceau a bien roulé ?
+maman|Le bateau a bien flotté ?
 enfant-m|Oui, maman.
-narrateur|Le petit cerceau s'arrête près du tapis.
-narrateur|Mila le reprend, tout doux.
-narrateur|Nino attend son tour.
-maman|Tu as attendu, Nino.
-maman|Bravo.</t>
-        </is>
-      </c>
-      <c r="AX4" t="inlineStr"/>
+narrateur|Une goutte tombe de la feuille.
+narrateur|Elle fait un rond dans l'eau.
+narrateur|La tarte ne fume plus.
+narrateur|Elle sent encore le beurre.
+enfant-m|Elle est prête ?
+maman|Presque.
+maman|Un bateau encore, si vous voulez.
+copine|Encore un.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1776,12 +1777,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>On range les cerceaux ? Oui. Maman glisse les cerceaux sous le canapé. Nino pose le panier près de la porte. Une pomme brille encore. Le salon sent le fruit et le tapis chaud. À demain. À demain. Bravo. Tu as invité. Vous avez joué ensemble. Le salon redevient calme.</t>
+          <t>On range les pommes sur l'assiette ? Oui. Nino pose une pomme. Mila pose l'autre. Les voiles de feuilles restent à côté. Tu as fini de poser les bateaux ? Oui, maman. Maman vide la bassine, tout bas. L'eau part dans l'herbe. À demain. À demain. La pierre sous la tarte est sèche. Le jardin sent le fruit et le beurre.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Maman range les cerceaux. Lila et Tom se disent à de&lt;emphasis level="moderate"&gt;main&lt;/emphasis&gt;.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>On range les pommes sur l'assiette ? Oui. Nino pose une pomme. Mila pose l'autre. Les voiles de feuilles restent à côté. Tu as fini de poser les bateaux ? Oui, maman. Maman vide la bassine, tout bas. L'eau part dans l'herbe. À demain. À demain. La pierre sous la tarte est sèche. Le jardin sent le fruit et le beurre.</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1844,7 +1845,7 @@
         <v>0.96</v>
       </c>
       <c r="AB5" s="2" t="n">
-        <v>1.12</v>
+        <v>1.22</v>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
@@ -1916,21 +1917,21 @@
       <c r="AV5" s="2" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>maman|On range les cerceaux ?
+          <t>maman|On range les pommes sur l'assiette ?
 enfant-m|Oui.
-narrateur|Maman glisse les cerceaux sous le canapé.
-narrateur|Nino pose le panier près de la porte.
-narrateur|Une pomme brille encore.
-narrateur|Le salon sent le fruit et le tapis chaud.
+narrateur|Nino pose une pomme.
+narrateur|Mila pose l'autre.
+narrateur|Les voiles de feuilles restent à côté.
+maman|Tu as fini de poser les bateaux ?
+enfant-m|Oui, maman.
+narrateur|Maman vide la bassine, tout bas.
+narrateur|L'eau part dans l'herbe.
 copine|À demain.
 enfant-m|À demain.
-maman|Bravo.
-maman|Tu as invité.
-maman|Vous avez joué ensemble.
-narrateur|Le salon redevient calme.</t>
-        </is>
-      </c>
-      <c r="AX5" t="inlineStr"/>
+narrateur|La pierre sous la tarte est sèche.
+narrateur|Le jardin sent le fruit et le beurre.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1955,12 +1956,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>On a rangé les pommes. On a joué ensemble. Bravo. Tu as fait du bon travail. L'histoire est finie.</t>
+          <t>Les bateaux ont flotté. On a joué ensemble. Bravo, Nino. La tarte attend encore un peu. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="low"&gt;L'histoire est finie.&lt;/prosody&gt;&lt;break time="600ms"/&gt;&lt;/speak&gt;</t>
+          <t>Les bateaux ont flotté. On a joué ensemble. Bravo, Nino. La tarte attend encore un peu. L'histoire est finie.</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -2023,7 +2024,7 @@
         <v>0.92</v>
       </c>
       <c r="AB6" s="2" t="n">
-        <v>1.2</v>
+        <v>1.28</v>
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
@@ -2095,14 +2096,13 @@
       <c r="AV6" s="2" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>enfant-m|On a rangé les pommes.
+          <t>enfant-m|Les bateaux ont flotté.
 enfant-m|On a joué ensemble.
-maman|Bravo.
-maman|Tu as fait du bon travail.
+maman|Bravo, Nino.
+narrateur|La tarte attend encore un peu.
 narrateur|L'histoire est finie.</t>
         </is>
       </c>
-      <c r="AX6" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2121,7 +2121,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A9"/>
+  <dimension ref="A1:A10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2187,6 +2187,13 @@
       <c r="A9" t="inlineStr">
         <is>
           <t>F-NAR-009 ouverture du monde, fusion agents</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-DIF.COR.001-03.xlsx
+++ b/stories/arbres/ATOM-DIF.COR.001-03.xlsx
@@ -1956,12 +1956,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>Les bateaux ont flotté. On a joué ensemble. Bravo, Nino. La tarte attend encore un peu. L'histoire est finie.</t>
+          <t>Les bateaux ont flotté. On a joué ensemble. Bravo, Nino. La tarte attend encore un peu.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>Les bateaux ont flotté. On a joué ensemble. Bravo, Nino. La tarte attend encore un peu. L'histoire est finie.</t>
+          <t>Les bateaux ont flotté. On a joué ensemble. Bravo, Nino. La tarte attend encore un peu.</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -2099,8 +2099,7 @@
           <t>enfant-m|Les bateaux ont flotté.
 enfant-m|On a joué ensemble.
 maman|Bravo, Nino.
-narrateur|La tarte attend encore un peu.
-narrateur|L'histoire est finie.</t>
+narrateur|La tarte attend encore un peu.</t>
         </is>
       </c>
     </row>
@@ -2121,7 +2120,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A10"/>
+  <dimension ref="A1:A11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2192,6 +2191,13 @@
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
         <is>
           <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>

--- a/stories/arbres/ATOM-DIF.COR.001-03.xlsx
+++ b/stories/arbres/ATOM-DIF.COR.001-03.xlsx
@@ -676,7 +676,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>jardin puis salon</t>
+          <t>pierre du jardin, tarte qui refroidit, bassine sur la marche</t>
         </is>
       </c>
     </row>
@@ -688,7 +688,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Lila, Tom, maman</t>
+          <t>Nino, Mila, maman</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-DIF.COR.001-03.xlsx
+++ b/stories/arbres/ATOM-DIF.COR.001-03.xlsx
@@ -688,7 +688,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Nino, Mila, maman</t>
+          <t>Nino, Mila, papa, maman</t>
         </is>
       </c>
     </row>
@@ -846,7 +846,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Nino veut faire flotter des bateaux de pomme. La bassine est trop haute pour Mila. Ils la posent sur la marche et soufflent ensemble jusqu'au bord.</t>
+          <t>Une odeur de beurre monte de la pierre du jardin. Sur le bord, un éclat de bassine luit. Nino veut le bateau de pomme jusqu'au bord d'en face, maintenant. Il pousse trop fort depuis la table : la pomme s'arrête au milieu. Mila n'atteint pas. Sourire parti. Papa s'accroupit. Il refuse de foncer, pose la bassine sur la marche, souffle avec Mila. Merci vécu. Un second bateau tape le bord. Il attend. L'éclat de bassine tient.</t>
         </is>
       </c>
     </row>
@@ -1189,17 +1189,17 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>La tarte aux pommes fume encore. Elle sent le beurre. Maman l'a posée sur la pierre. La pierre est froide, sous le plat. Une pomme tombée attend dans l'herbe. Une feuille y est collée. Tu as senti la tarte, Nino ? Oui, maman. Elle est chaude. Elle va refroidir. Je veux un bateau de pomme. Dans la bassine ? Oui. En ce moment, Nino prend la pomme. Elle est collante, un peu sucrée. Maman pose une bassine d'eau. La bassine est sur la table. Mila arrive sous l'arbre. Mila est plus petite. Nino est plus grand. Ils ont des tailles différentes. Tu veux le bateau avec moi ? Oui. Mila lève les mains. La table est trop haute pour elle. Elle n'atteint pas. On pose la bassine plus bas. Maman la pose sur la marche. L'eau tremble, puis s'arrête. Vous jouez ensemble, là. On peut jouer ensemble. Nino met une feuille en voile. Mila pousse la pomme dans l'eau. La pomme tourne, tout seule. Elle fait des ronds ! Oui. On souffle ? Oui. Ils soufflent ensemble. L'eau fait de toutes petites vagues. Ça sent encore le beurre, derrière. La tarte attend. Le bateau d'abord.</t>
+          <t>Une odeur de beurre monte de la pierre. La pierre du jardin est froide, sous le plat. La tarte aux pommes fume, tiède. Elle sent le beurre, papa. Tu l'as vue, sur la pierre ? Oui, papa. Elle va refroidir, Nino. Une pomme tombée attend dans l'herbe. Une feuille y est collée, un peu sucrée. L'herbe pique un peu, sous les pieds. Une bassine d'eau attend sur la marche. Le soleil tape le bord, étroit. Un rond blanc danse dans l'eau. Sur le bord, un éclat de bassine luit. Il brille, maman. Tu le vois, sur le bord ? Oui, il brille. C'est le bord de la bassine. Je veux un bateau, maintenant ! Un bateau de pomme ? Oui, jusqu'au bord, là-bas. Jusqu'au bord d'en face ? Oui, tout de suite ! En ce moment, Nino prend la pomme. Elle est collante, un peu sucrée. Il plante la feuille, en voile. Maman pose la bassine sur la table. La table est haute, près de l'arbre. Mila arrive sous l'arbre. Elle lève les mains vers l'eau. Tu viens ? Oui. Mila se dresse sur les pointes. Ses doigts n'atteignent pas l'eau. Je n'arrive pas. Moi, je pousse ! Nino pousse trop fort, trop loin. La pomme tourne, puis s'arrête au milieu. Elle n'arrive pas. L'éclat de bassine saute près de l'eau. Le sourire de Nino disparaît. Dans sa poitrine, l'envie et l'inquiétude se bousculent. Ses épaules tombent un peu. Papa s'accroupit à la même hauteur. Tu veux le bateau jusqu'au bord ? Oui, papa. Avec Mila, Nino ? Oui. Elle n'atteint pas la table ? Non.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>La tarte aux pommes fume encore. Elle sent le beurre. Maman l'a posée sur la pierre. La pierre est froide, sous le plat. Une pomme tombée attend dans l'herbe. Une feuille y est collée. Tu as senti la tarte, Nino ? Oui, maman. Elle est chaude. Elle va refroidir. Je veux un bateau de pomme. Dans la bassine ? Oui. En ce moment, Nino prend la pomme. Elle est collante, un peu sucrée. Maman pose une bassine d'eau. La bassine est sur la table. Mila arrive sous l'arbre. Mila est plus petite. Nino est plus grand. Ils ont des tailles différentes. Tu veux le bateau avec moi ? Oui. Mila lève les mains. La table est trop haute pour elle. Elle n'atteint pas. On pose la bassine plus bas. Maman la pose sur la marche. L'eau tremble, puis s'arrête. Vous jouez ensemble, là. On peut jouer ensemble. Nino met une feuille en voile. Mila pousse la pomme dans l'eau. La pomme tourne, tout seule. Elle fait des ronds ! Oui. On souffle ? Oui. Ils soufflent ensemble. L'eau fait de toutes petites vagues. Ça sent encore le beurre, derrière. La tarte attend. Le bateau d'abord.</t>
+          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Une odeur de beurre monte de la pierre. La pierre du jardin est froide, sous le plat. La tarte aux pommes fume, tiède. Elle sent le beurre, papa. Tu l'as vue, sur la pierre ? Oui, papa. Elle va refroidir, Nino. Une pomme tombée attend dans l'herbe. Une feuille y est collée, un peu sucrée. L'herbe pique un peu, sous les pieds. Une bassine d'eau attend sur la marche. Le soleil tape le bord, étroit. Un rond blanc danse dans l'eau. Sur le bord, un &lt;emphasis level="moderate"&gt;éclat de bassine&lt;/emphasis&gt; luit. Il brille, maman. Tu le vois, sur le bord ? Oui, il brille. C'est le bord de la bassine. Je veux un bateau, maintenant ! Un bateau de pomme ? Oui, jusqu'au bord, là-bas. Jusqu'au bord d'en face ? Oui, tout de suite ! En ce moment, Nino prend la pomme. Elle est collante, un peu sucrée. Il plante la feuille, en voile. Maman pose la bassine sur la table. La table est haute, près de l'arbre. Mila arrive sous l'arbre. Elle lève les mains vers l'eau. Tu viens ? Oui. Mila se dresse sur les pointes. Ses doigts n'atteignent pas l'eau. Je n'arrive pas. Moi, je pousse ! Nino pousse trop fort, trop loin. La pomme tourne, puis s'arrête au milieu. Elle n'arrive pas. L'éclat de bassine saute près de l'eau. Le sourire de Nino disparaît. Dans sa poitrine, l'envie et l'inquiétude se bousculent. Ses épaules tombent un peu. Papa s'accroupit à la même hauteur. Tu veux le bateau jusqu'au bord ? Oui, papa. Avec Mila, Nino ? Oui. Elle n'atteint pas la table ? Non.&lt;/prosody&gt;&lt;break time="500ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>Maman emmène Lila dans le jardin. Tom arrive. Tom est plus grand. Lila est plus petite. Ils ont des &lt;emphasis&gt;tailles&lt;/emphasis&gt; différentes. Un panier de pommes est posé. Lila hésite. Elle se dit que Tom atteint plus haut. Maman s'accroupit. Maman dit : les tailles différentes n'empêchent pas le jeu. On invite. On joue ensemble. Lila va vers Tom. Elle dit : tu veux le panier avec moi. Tom dit : oui. Tom tend une pomme tout près. Lila la pose. Ils font un tas. Parfois Tom pose plus haut. Parfois Lila pose tout bas. Les deux façons marchent. Plus tard, ils rentrent au salon. Maman sort des cerceaux. Tom enfile le grand. Lila enfile le petit. Lila se souvient. Elle invite. Tom dit oui. Ils font rouler les cerceaux. Maman dit : au jardin, puis ici. C'est la même leçon. Petit ou grand, on invite. On joue ensemble. Lila et Tom tapent dans leurs mains. Les tailles différentes sont encore là. Le jeu aussi. [pause]</t>
+          <t>Une odeur de beurre monte de la pierre. La pierre du jardin est froide, sous le plat. La tarte aux pommes fume, tiède. Elle sent le beurre, papa. Tu l'as vue, sur la pierre ? Oui, papa. Elle va refroidir, Nino. Une pomme tombée attend dans l'herbe. Une feuille y est collée, un peu sucrée. L'herbe pique un peu, sous les pieds. Une bassine d'eau attend sur la marche. Le soleil tape le bord, étroit. Un rond blanc danse dans l'eau. Sur le bord, un &lt;emphasis&gt;éclat de bassine&lt;/emphasis&gt; luit. Il brille, maman. Tu le vois, sur le bord ? Oui, il brille. C'est le bord de la bassine. Je veux un bateau, maintenant ! Un bateau de pomme ? Oui, jusqu'au bord, là-bas. Jusqu'au bord d'en face ? Oui, tout de suite ! En ce moment, Nino prend la pomme. Elle est collante, un peu sucrée. Il plante la feuille, en voile. Maman pose la bassine sur la table. La table est haute, près de l'arbre. Mila arrive sous l'arbre. Elle lève les mains vers l'eau. Tu viens ? Oui. Mila se dresse sur les pointes. Ses doigts n'atteignent pas l'eau. Je n'arrive pas. Moi, je pousse ! Nino pousse trop fort, trop loin. La pomme tourne, puis s'arrête au milieu. Elle n'arrive pas. L'éclat de bassine saute près de l'eau. Le sourire de Nino disparaît. Dans sa poitrine, l'envie et l'inquiétude se bousculent. Ses épaules tombent un peu. Papa s'accroupit à la même hauteur. Tu veux le bateau jusqu'au bord ? Oui, papa. Avec Mila, Nino ? Oui. Elle n'atteint pas la table ? Non. [pause]</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr"/>
@@ -1246,7 +1246,7 @@
         </is>
       </c>
       <c r="Y2" s="2" t="n">
-        <v>148</v>
+        <v>142</v>
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
@@ -1254,10 +1254,10 @@
         </is>
       </c>
       <c r="AA2" s="2" t="n">
-        <v>0.96</v>
+        <v>0.98</v>
       </c>
       <c r="AB2" s="2" t="n">
-        <v>1.22</v>
+        <v>1.12</v>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
@@ -1280,30 +1280,30 @@
       </c>
       <c r="AH2" s="2" t="inlineStr">
         <is>
-          <t>tailles</t>
+          <t>éclat de bassine</t>
         </is>
       </c>
       <c r="AI2" s="2" t="n">
         <v>0</v>
       </c>
       <c r="AJ2" s="2" t="n">
-        <v>400</v>
+        <v>500</v>
       </c>
       <c r="AK2" s="2" t="n">
-        <v>280</v>
+        <v>260</v>
       </c>
       <c r="AL2" s="2" t="inlineStr">
         <is>
-          <t>calm</t>
+          <t>warm</t>
         </is>
       </c>
       <c r="AM2" s="2" t="inlineStr">
         <is>
-          <t>level</t>
+          <t>storytelling</t>
         </is>
       </c>
       <c r="AN2" s="2" t="n">
-        <v>0.333</v>
+        <v>0.36</v>
       </c>
       <c r="AO2" s="2" t="inlineStr"/>
       <c r="AP2" s="2" t="inlineStr">
@@ -1312,10 +1312,10 @@
         </is>
       </c>
       <c r="AQ2" s="2" t="n">
-        <v>0.96</v>
+        <v>0.98</v>
       </c>
       <c r="AR2" s="2" t="n">
-        <v>0.96</v>
+        <v>0.98</v>
       </c>
       <c r="AS2" s="2" t="n">
         <v>100</v>
@@ -1326,52 +1326,68 @@
       <c r="AU2" s="2" t="n">
         <v>8</v>
       </c>
-      <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AV2" s="2" t="inlineStr">
+        <is>
+          <t>arc=installation; intention=émerveiller puis tendre; emotion=impatience puis découragement; intensite=2; destinataire=enfant; sous_texte=il_veut_le_bateau_jusqu_au_bord_maintenant; tempo=naturel puis resserré; sourire=léger puis aucun; respiration=ample puis retenue</t>
+        </is>
+      </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>narrateur|La tarte aux pommes fume encore.
-narrateur|Elle sent le beurre.
-narrateur|Maman l'a posée sur la pierre.
-narrateur|La pierre est froide, sous le plat.
+          <t>narrateur|Une odeur de beurre monte de la pierre.
+narrateur|La pierre du jardin est froide, sous le plat.
+narrateur|La tarte aux pommes fume, tiède.
+enfant-m|Elle sent le beurre, papa.
+papa|Tu l'as vue, sur la pierre ?
+enfant-m|Oui, papa.
+maman|Elle va refroidir, Nino.
 narrateur|Une pomme tombée attend dans l'herbe.
-narrateur|Une feuille y est collée.
-maman|Tu as senti la tarte, Nino ?
-enfant-m|Oui, maman.
-enfant-m|Elle est chaude.
-maman|Elle va refroidir.
-enfant-m|Je veux un bateau de pomme.
-maman|Dans la bassine ?
-enfant-m|Oui.
+narrateur|Une feuille y est collée, un peu sucrée.
+narrateur|L'herbe pique un peu, sous les pieds.
+narrateur|Une bassine d'eau attend sur la marche.
+narrateur|Le soleil tape le bord, étroit.
+narrateur|Un rond blanc danse dans l'eau.
+narrateur|Sur le bord, un éclat de bassine luit.
+enfant-m|Il brille, maman.
+maman|Tu le vois, sur le bord ?
+enfant-m|Oui, il brille.
+papa|C'est le bord de la bassine.
+enfant-m|Je veux un bateau, maintenant !
+maman|Un bateau de pomme ?
+enfant-m|Oui, jusqu'au bord, là-bas.
+papa|Jusqu'au bord d'en face ?
+enfant-m|Oui, tout de suite !
 narrateur|En ce moment, Nino prend la pomme.
 narrateur|Elle est collante, un peu sucrée.
-narrateur|Maman pose une bassine d'eau.
-narrateur|La bassine est sur la table.
+narrateur|Il plante la feuille, en voile.
+narrateur|Maman pose la bassine sur la table.
+narrateur|La table est haute, près de l'arbre.
 narrateur|Mila arrive sous l'arbre.
-narrateur|Mila est plus petite.
-narrateur|Nino est plus grand.
-narrateur|Ils ont des tailles différentes.
-enfant-m|Tu veux le bateau avec moi ?
+narrateur|Elle lève les mains vers l'eau.
+enfant-m|Tu viens ?
 copine|Oui.
-narrateur|Mila lève les mains.
-narrateur|La table est trop haute pour elle.
-enfant-m|Elle n'atteint pas.
-maman|On pose la bassine plus bas.
-narrateur|Maman la pose sur la marche.
-narrateur|L'eau tremble, puis s'arrête.
-maman|Vous jouez ensemble, là.
-maman|On peut jouer ensemble.
-narrateur|Nino met une feuille en voile.
-narrateur|Mila pousse la pomme dans l'eau.
-narrateur|La pomme tourne, tout seule.
-enfant-m|Elle fait des ronds !
-maman|Oui.
-copine|On souffle ?
+narrateur|Mila se dresse sur les pointes.
+narrateur|Ses doigts n'atteignent pas l'eau.
+copine|Je n'arrive pas.
+enfant-m|Moi, je pousse !
+narrateur|Nino pousse trop fort, trop loin.
+narrateur|La pomme tourne, puis s'arrête au milieu.
+enfant-m|Elle n'arrive pas.
+narrateur|L'éclat de bassine saute près de l'eau.
+narrateur|Le sourire de Nino disparaît.
+narrateur|Dans sa poitrine, l'envie et l'inquiétude se bousculent.
+narrateur|Ses épaules tombent un peu.
+narrateur|Papa s'accroupit à la même hauteur.
+papa|Tu veux le bateau jusqu'au bord ?
+enfant-m|Oui, papa.
+maman|Avec Mila, Nino ?
 enfant-m|Oui.
-narrateur|Ils soufflent ensemble.
-narrateur|L'eau fait de toutes petites vagues.
-narrateur|Ça sent encore le beurre, derrière.
-maman|La tarte attend.
-enfant-m|Le bateau d'abord.</t>
+papa|Elle n'atteint pas la table ?
+enfant-m|Non.</t>
+        </is>
+      </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>tarte,pierre,bassine</t>
         </is>
       </c>
     </row>
@@ -1403,12 +1419,12 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>Nino est plus grand. Mila est plus petite. Que font-ils ?</t>
+          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Nino est plus grand. &lt;emphasis level="moderate"&gt;Mila&lt;/emphasis&gt; est plus petite. Que font-ils ?&lt;/prosody&gt;&lt;break time="700ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>Lila est plus petite. Tom est plus grand. Que font-ils ?</t>
+          <t>&lt;soft&gt;&lt;slow&gt;Nino est plus grand. &lt;emphasis&gt;Mila&lt;/emphasis&gt; est plus petite. Que font-ils ?&lt;/slow&gt;&lt;/soft&gt; [pause]</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
@@ -1418,7 +1434,7 @@
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>jouer ensemble | ensemble | ils jouent | inviter | le panier</t>
+          <t>jouer ensemble | ensemble | ils jouent | on joue | souffler ensemble</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
@@ -1471,7 +1487,7 @@
         </is>
       </c>
       <c r="Y3" s="2" t="n">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
@@ -1479,10 +1495,10 @@
         </is>
       </c>
       <c r="AA3" s="2" t="n">
-        <v>0.9</v>
+        <v>0.86</v>
       </c>
       <c r="AB3" s="2" t="n">
-        <v>1.24</v>
+        <v>1.27</v>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
@@ -1497,34 +1513,38 @@
       <c r="AE3" s="2" t="inlineStr"/>
       <c r="AF3" s="2" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>soft</t>
         </is>
       </c>
       <c r="AG3" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH3" s="2" t="inlineStr"/>
+        <v>-2</v>
+      </c>
+      <c r="AH3" s="2" t="inlineStr">
+        <is>
+          <t>Mila</t>
+        </is>
+      </c>
       <c r="AI3" s="2" t="n">
         <v>200</v>
       </c>
       <c r="AJ3" s="2" t="n">
-        <v>250</v>
+        <v>700</v>
       </c>
       <c r="AK3" s="2" t="n">
-        <v>280</v>
+        <v>320</v>
       </c>
       <c r="AL3" s="2" t="inlineStr">
         <is>
-          <t>warm</t>
+          <t>focused</t>
         </is>
       </c>
       <c r="AM3" s="2" t="inlineStr">
         <is>
-          <t>rise</t>
+          <t>rising</t>
         </is>
       </c>
       <c r="AN3" s="2" t="n">
-        <v>0.333</v>
+        <v>0.32</v>
       </c>
       <c r="AO3" s="2" t="inlineStr"/>
       <c r="AP3" s="2" t="inlineStr">
@@ -1533,23 +1553,23 @@
         </is>
       </c>
       <c r="AQ3" s="2" t="n">
-        <v>0.9</v>
+        <v>0.86</v>
       </c>
       <c r="AR3" s="2" t="n">
-        <v>0.9</v>
+        <v>0.86</v>
       </c>
       <c r="AS3" s="2" t="n">
-        <v>100</v>
+        <v>82</v>
       </c>
       <c r="AT3" s="2" t="n">
         <v>50</v>
       </c>
       <c r="AU3" s="2" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="AV3" s="2" t="inlineStr">
         <is>
-          <t>question d'écoute, ne change pas le cours</t>
+          <t>arc=indice; intention=faire_deviner; emotion=attention; intensite=1; destinataire=enfant; sous_texte=plus_grand_plus_petite_ils_jouent_ensemble; tempo=suspendu; sourire=aucun; respiration=courte_avant_question</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
@@ -1583,17 +1603,17 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Le bateau arrive au bord. Mila le rattrape tout bas. Nino en prépare un autre. Une feuille verte, une pomme jaune. Deux bateaux, maintenant. Oui. Les deux façons marchent. Parfois Nino pousse plus loin. Parfois Mila pousse tout près. Les pommes se croisent. La mienne a tourné ! La mienne aussi. Vous avez des tailles différentes. Et vous jouez ensemble. Le bateau a bien flotté ? Oui, maman. Une goutte tombe de la feuille. Elle fait un rond dans l'eau. La tarte ne fume plus. Elle sent encore le beurre. Elle est prête ? Presque. Un bateau encore, si vous voulez. Encore un.</t>
+          <t>Nino veut pousser, d'un coup. Nino refuse de foncer. Personne ne parle. Il observe l'eau, un instant. Il écoute le jardin, près de la pierre. Sur le bord, l'éclat de bassine revient. On pose la bassine, plus bas. Sur la marche ? Oui, papa. Papa pose la bassine sur la marche. L'eau tremble, puis s'arrête. Mila touche l'eau, du bout des doigts. Elle est froide. On souffle ? Oui. Ils soufflent du même côté de l'eau. La pomme glisse, lente, vers le bord. Elle arrive ! Je la tiens. Mila rattrape la pomme, près d'elle. Nino reste de son côté, plus haut. Merci, Nino. Papa a regardé jusqu'au bout. Le ventre de Nino se desserre. Un autre bateau ? La tarte attend un peu. Le bateau d'abord. Tes pieds sont sur la marche ? Oui, maman. Et Mila ? Moi aussi.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>Le bateau arrive au bord. Mila le rattrape tout bas. Nino en prépare un autre. Une feuille verte, une pomme jaune. Deux bateaux, maintenant. Oui. Les deux façons marchent. Parfois Nino pousse plus loin. Parfois Mila pousse tout près. Les pommes se croisent. La mienne a tourné ! La mienne aussi. Vous avez des tailles différentes. Et vous jouez ensemble. Le bateau a bien flotté ? Oui, maman. Une goutte tombe de la feuille. Elle fait un rond dans l'eau. La tarte ne fume plus. Elle sent encore le beurre. Elle est prête ? Presque. Un bateau encore, si vous voulez. Encore un.</t>
+          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Nino veut pousser, d'un coup. Nino refuse de foncer. Personne ne parle. Il observe l'eau, un instant. Il écoute le jardin, près de la pierre. Sur le bord, l'éclat de bassine revient. On pose la bassine, plus bas. Sur la &lt;emphasis level="moderate"&gt;marche&lt;/emphasis&gt; ? Oui, papa. Papa pose la bassine sur la marche. L'eau tremble, puis s'arrête. Mila touche l'eau, du bout des doigts. Elle est froide. On souffle ? Oui. Ils soufflent du même côté de l'eau. La pomme glisse, lente, vers le bord. Elle arrive ! Je la tiens. Mila rattrape la pomme, près d'elle. Nino reste de son côté, plus haut. Merci, Nino. Papa a regardé jusqu'au bout. Le ventre de Nino se desserre. Un autre bateau ? La tarte attend un peu. Le bateau d'abord. Tes pieds sont sur la marche ? Oui, maman. Et Mila ? Moi aussi.&lt;/prosody&gt;&lt;break time="560ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>Lila a invité. Tom a tendu la pomme tout près. Ils ont des &lt;emphasis&gt;tailles&lt;/emphasis&gt; différentes. Ils ont joué ensemble. [pause]</t>
+          <t>Nino veut pousser, d'un coup. Nino refuse de foncer. Personne ne parle. Il observe l'eau, un instant. Il écoute le jardin, près de la pierre. Sur le bord, l'éclat de bassine revient. On pose la bassine, plus bas. Sur la &lt;emphasis&gt;marche&lt;/emphasis&gt; ? Oui, papa. Papa pose la bassine sur la marche. L'eau tremble, puis s'arrête. Mila touche l'eau, du bout des doigts. Elle est froide. On souffle ? Oui. Ils soufflent du même côté de l'eau. La pomme glisse, lente, vers le bord. Elle arrive ! Je la tiens. Mila rattrape la pomme, près d'elle. Nino reste de son côté, plus haut. Merci, Nino. Papa a regardé jusqu'au bout. Le ventre de Nino se desserre. Un autre bateau ? La tarte attend un peu. Le bateau d'abord. Tes pieds sont sur la marche ? Oui, maman. Et Mila ? Moi aussi. [pause]</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr"/>
@@ -1640,7 +1660,7 @@
         </is>
       </c>
       <c r="Y4" s="2" t="n">
-        <v>148</v>
+        <v>140</v>
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
@@ -1648,10 +1668,10 @@
         </is>
       </c>
       <c r="AA4" s="2" t="n">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="AB4" s="2" t="n">
-        <v>1.22</v>
+        <v>1.14</v>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
@@ -1674,30 +1694,30 @@
       </c>
       <c r="AH4" s="2" t="inlineStr">
         <is>
-          <t>tailles</t>
+          <t>marche</t>
         </is>
       </c>
       <c r="AI4" s="2" t="n">
         <v>200</v>
       </c>
       <c r="AJ4" s="2" t="n">
-        <v>450</v>
+        <v>560</v>
       </c>
       <c r="AK4" s="2" t="n">
-        <v>280</v>
+        <v>270</v>
       </c>
       <c r="AL4" s="2" t="inlineStr">
         <is>
-          <t>calm</t>
+          <t>bright</t>
         </is>
       </c>
       <c r="AM4" s="2" t="inlineStr">
         <is>
-          <t>level</t>
+          <t>falling</t>
         </is>
       </c>
       <c r="AN4" s="2" t="n">
-        <v>0.333</v>
+        <v>0.35</v>
       </c>
       <c r="AO4" s="2" t="inlineStr"/>
       <c r="AP4" s="2" t="inlineStr">
@@ -1706,10 +1726,10 @@
         </is>
       </c>
       <c r="AQ4" s="2" t="n">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="AR4" s="2" t="n">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="AS4" s="2" t="n">
         <v>100</v>
@@ -1722,35 +1742,47 @@
       </c>
       <c r="AV4" s="2" t="inlineStr">
         <is>
-          <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
+          <t>arc=résolution; intention=faire_vivre_le_geste; emotion=retenue puis fierté_calme; intensite=2; destinataire=enfant; sous_texte=bassine_sur_la_marche_ils_soufflent; tempo=naturel; sourire=léger; respiration=relâchée</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>narrateur|Le bateau arrive au bord.
-narrateur|Mila le rattrape tout bas.
-narrateur|Nino en prépare un autre.
-narrateur|Une feuille verte, une pomme jaune.
-enfant-m|Deux bateaux, maintenant.
-maman|Oui.
-maman|Les deux façons marchent.
-narrateur|Parfois Nino pousse plus loin.
-narrateur|Parfois Mila pousse tout près.
-narrateur|Les pommes se croisent.
-copine|La mienne a tourné !
-enfant-m|La mienne aussi.
-maman|Vous avez des tailles différentes.
-maman|Et vous jouez ensemble.
-maman|Le bateau a bien flotté ?
+          <t>narrateur|Nino veut pousser, d'un coup.
+narrateur|Nino refuse de foncer.
+narrateur|Personne ne parle.
+narrateur|Il observe l'eau, un instant.
+narrateur|Il écoute le jardin, près de la pierre.
+narrateur|Sur le bord, l'éclat de bassine revient.
+enfant-m|On pose la bassine, plus bas.
+papa|Sur la marche ?
+enfant-m|Oui, papa.
+narrateur|Papa pose la bassine sur la marche.
+narrateur|L'eau tremble, puis s'arrête.
+narrateur|Mila touche l'eau, du bout des doigts.
+copine|Elle est froide.
+enfant-m|On souffle ?
+copine|Oui.
+narrateur|Ils soufflent du même côté de l'eau.
+narrateur|La pomme glisse, lente, vers le bord.
+enfant-m|Elle arrive !
+copine|Je la tiens.
+narrateur|Mila rattrape la pomme, près d'elle.
+narrateur|Nino reste de son côté, plus haut.
+papa|Merci, Nino.
+narrateur|Papa a regardé jusqu'au bout.
+narrateur|Le ventre de Nino se desserre.
+enfant-m|Un autre bateau ?
+maman|La tarte attend un peu.
+enfant-m|Le bateau d'abord.
+maman|Tes pieds sont sur la marche ?
 enfant-m|Oui, maman.
-narrateur|Une goutte tombe de la feuille.
-narrateur|Elle fait un rond dans l'eau.
-narrateur|La tarte ne fume plus.
-narrateur|Elle sent encore le beurre.
-enfant-m|Elle est prête ?
-maman|Presque.
-maman|Un bateau encore, si vous voulez.
-copine|Encore un.</t>
+papa|Et Mila ?
+copine|Moi aussi.</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>eau,pomme</t>
         </is>
       </c>
     </row>
@@ -1777,17 +1809,17 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>On range les pommes sur l'assiette ? Oui. Nino pose une pomme. Mila pose l'autre. Les voiles de feuilles restent à côté. Tu as fini de poser les bateaux ? Oui, maman. Maman vide la bassine, tout bas. L'eau part dans l'herbe. À demain. À demain. La pierre sous la tarte est sèche. Le jardin sent le fruit et le beurre.</t>
+          <t>Nino prépare une autre pomme. Une feuille verte tient, collée. Celle-là, plus loin ! Il pousse trop vite, du haut de la marche. L'eau saute contre le bord. La pomme tape le bord, puis revient. Oh. Mila retire les mains. Non. Le sourire ne revient pas. Nino veut rattraper, d'un coup. Nino refuse de foncer. Ses épaules se serrent un peu. Ça tape, dans sa poitrine. Personne ne dit la suite. Il regarde le bord, il écoute l'eau. Un oiseau passe, loin. On souffle, Mila ? Mila ne dit rien. Elle garde les mains sur ses genoux. D'accord. Nino attend. Plus tard. Oui. La pomme se cale, sans tourner. Mila avance un doigt. Elle pousse près d'elle, puis s'arrête. D'accord. Ils soufflent, chacun de son bord. Les deux pommes se croisent. La mienne a tourné ! La mienne aussi. La tarte ne fume plus. Elle est prête ? Presque. Tes mains sont dans l'eau ? Oui, papa.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>On range les pommes sur l'assiette ? Oui. Nino pose une pomme. Mila pose l'autre. Les voiles de feuilles restent à côté. Tu as fini de poser les bateaux ? Oui, maman. Maman vide la bassine, tout bas. L'eau part dans l'herbe. À demain. À demain. La pierre sous la tarte est sèche. Le jardin sent le fruit et le beurre.</t>
+          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Nino prépare une autre &lt;emphasis level="moderate"&gt;pomme&lt;/emphasis&gt;. Une feuille verte tient, collée. Celle-là, plus loin ! Il pousse trop vite, du haut de la marche. L'eau saute contre le bord. La pomme tape le bord, puis revient. Oh. Mila retire les mains. Non. Le sourire ne revient pas. Nino veut rattraper, d'un coup. Nino refuse de foncer. Ses épaules se serrent un peu. Ça tape, dans sa poitrine. Personne ne dit la suite. Il regarde le bord, il écoute l'eau. Un oiseau passe, loin. On souffle, Mila ? Mila ne dit rien. Elle garde les mains sur ses genoux. D'accord. Nino attend. Plus tard. Oui. La pomme se cale, sans tourner. Mila avance un doigt. Elle pousse près d'elle, puis s'arrête. D'accord. Ils soufflent, chacun de son bord. Les deux pommes se croisent. La mienne a tourné ! La mienne aussi. La tarte ne fume plus. Elle est prête ? Presque. Tes mains sont dans l'eau ? Oui, papa.&lt;/prosody&gt;&lt;break time="420ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>Maman range les cerceaux. Lila et Tom se disent à de&lt;emphasis&gt;main&lt;/emphasis&gt;. [pause]</t>
+          <t>Nino prépare une autre &lt;emphasis&gt;pomme&lt;/emphasis&gt;. Une feuille verte tient, collée. Celle-là, plus loin ! Il pousse trop vite, du haut de la marche. L'eau saute contre le bord. La pomme tape le bord, puis revient. Oh. Mila retire les mains. Non. Le sourire ne revient pas. Nino veut rattraper, d'un coup. Nino refuse de foncer. Ses épaules se serrent un peu. Ça tape, dans sa poitrine. Personne ne dit la suite. Il regarde le bord, il écoute l'eau. Un oiseau passe, loin. On souffle, Mila ? Mila ne dit rien. Elle garde les mains sur ses genoux. D'accord. Nino attend. Plus tard. Oui. La pomme se cale, sans tourner. Mila avance un doigt. Elle pousse près d'elle, puis s'arrête. D'accord. Ils soufflent, chacun de son bord. Les deux pommes se croisent. La mienne a tourné ! La mienne aussi. La tarte ne fume plus. Elle est prête ? Presque. Tes mains sont dans l'eau ? Oui, papa. [pause]</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr"/>
@@ -1834,7 +1866,7 @@
         </is>
       </c>
       <c r="Y5" s="2" t="n">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
@@ -1842,10 +1874,10 @@
         </is>
       </c>
       <c r="AA5" s="2" t="n">
-        <v>0.96</v>
+        <v>1</v>
       </c>
       <c r="AB5" s="2" t="n">
-        <v>1.22</v>
+        <v>1.1</v>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
@@ -1868,30 +1900,30 @@
       </c>
       <c r="AH5" s="2" t="inlineStr">
         <is>
-          <t>main</t>
+          <t>pomme</t>
         </is>
       </c>
       <c r="AI5" s="2" t="n">
         <v>200</v>
       </c>
       <c r="AJ5" s="2" t="n">
-        <v>450</v>
+        <v>420</v>
       </c>
       <c r="AK5" s="2" t="n">
-        <v>280</v>
+        <v>250</v>
       </c>
       <c r="AL5" s="2" t="inlineStr">
         <is>
-          <t>calm</t>
+          <t>lively</t>
         </is>
       </c>
       <c r="AM5" s="2" t="inlineStr">
         <is>
-          <t>level</t>
+          <t>dynamic</t>
         </is>
       </c>
       <c r="AN5" s="2" t="n">
-        <v>0.333</v>
+        <v>0.37</v>
       </c>
       <c r="AO5" s="2" t="inlineStr"/>
       <c r="AP5" s="2" t="inlineStr">
@@ -1900,10 +1932,10 @@
         </is>
       </c>
       <c r="AQ5" s="2" t="n">
-        <v>0.96</v>
+        <v>1</v>
       </c>
       <c r="AR5" s="2" t="n">
-        <v>0.96</v>
+        <v>1</v>
       </c>
       <c r="AS5" s="2" t="n">
         <v>100</v>
@@ -1914,22 +1946,55 @@
       <c r="AU5" s="2" t="n">
         <v>8</v>
       </c>
-      <c r="AV5" s="2" t="inlineStr"/>
+      <c r="AV5" s="2" t="inlineStr">
+        <is>
+          <t>arc=action; intention=entraîner; emotion=élan puis prudence; intensite=2; destinataire=enfant; sous_texte=il_refuse_de_pousser_trop_vite_du_haut; tempo=vif puis posé; sourire=léger; respiration=courte</t>
+        </is>
+      </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>maman|On range les pommes sur l'assiette ?
+          <t>narrateur|Nino prépare une autre pomme.
+narrateur|Une feuille verte tient, collée.
+enfant-m|Celle-là, plus loin !
+narrateur|Il pousse trop vite, du haut de la marche.
+narrateur|L'eau saute contre le bord.
+narrateur|La pomme tape le bord, puis revient.
+enfant-m|Oh.
+narrateur|Mila retire les mains.
+copine|Non.
+narrateur|Le sourire ne revient pas.
+narrateur|Nino veut rattraper, d'un coup.
+narrateur|Nino refuse de foncer.
+narrateur|Ses épaules se serrent un peu.
+narrateur|Ça tape, dans sa poitrine.
+narrateur|Personne ne dit la suite.
+narrateur|Il regarde le bord, il écoute l'eau.
+narrateur|Un oiseau passe, loin.
+enfant-m|On souffle, Mila ?
+narrateur|Mila ne dit rien.
+narrateur|Elle garde les mains sur ses genoux.
+enfant-m|D'accord.
+narrateur|Nino attend.
+copine|Plus tard.
 enfant-m|Oui.
-narrateur|Nino pose une pomme.
-narrateur|Mila pose l'autre.
-narrateur|Les voiles de feuilles restent à côté.
-maman|Tu as fini de poser les bateaux ?
-enfant-m|Oui, maman.
-narrateur|Maman vide la bassine, tout bas.
-narrateur|L'eau part dans l'herbe.
-copine|À demain.
-enfant-m|À demain.
-narrateur|La pierre sous la tarte est sèche.
-narrateur|Le jardin sent le fruit et le beurre.</t>
+narrateur|La pomme se cale, sans tourner.
+narrateur|Mila avance un doigt.
+narrateur|Elle pousse près d'elle, puis s'arrête.
+enfant-m|D'accord.
+narrateur|Ils soufflent, chacun de son bord.
+narrateur|Les deux pommes se croisent.
+copine|La mienne a tourné !
+enfant-m|La mienne aussi.
+maman|La tarte ne fume plus.
+enfant-m|Elle est prête ?
+maman|Presque.
+papa|Tes mains sont dans l'eau ?
+enfant-m|Oui, papa.</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>feuille,eau</t>
         </is>
       </c>
     </row>
@@ -1956,17 +2021,17 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>Les bateaux ont flotté. On a joué ensemble. Bravo, Nino. La tarte attend encore un peu.</t>
+          <t>Ils restent près de la marche. Les voiles de feuilles restent mouillées. L'éclat est là, papa. Tu le vois sur le bord ? Oui, papa. On est bien, ici. La tarte sent le beurre, plus légère. Mes bateaux ont flotté. Jusqu'au bord, Nino. Oui, maman. Nino pose la joue près du bord. Le bord est tiède, un peu. C'est tiède. Tu le sens sur tes joues ? Oui, il est tiède. Une feuille porte une goutte d'eau. Dehors, le jardin s'endort. L'éclat de bassine tient sur le bord.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>Les bateaux ont flotté. On a joué ensemble. Bravo, Nino. La tarte attend encore un peu.</t>
+          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="-2st"&gt;Ils restent près de la marche. Les voiles de feuilles restent mouillées. L'éclat est là, papa. Tu le vois sur le bord ? Oui, papa. On est bien, ici. La tarte sent le beurre, plus légère. Mes bateaux ont flotté. Jusqu'au bord, Nino. Oui, maman. Nino pose la joue près du bord. Le bord est tiède, un peu. C'est tiède. Tu le sens sur tes joues ? Oui, il est tiède. Une feuille porte une goutte d'eau. Dehors, le jardin s'endort. L'&lt;emphasis level="moderate"&gt;éclat de bassine&lt;/emphasis&gt; tient sur le bord.&lt;/prosody&gt;&lt;break time="900ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>&lt;lower-pitch&gt;&lt;soft&gt;L'histoire est finie.&lt;/soft&gt;&lt;/lower-pitch&gt; [pause]</t>
+          <t>&lt;low-pitch&gt;&lt;soft&gt;&lt;slow&gt;Ils restent près de la marche. Les voiles de feuilles restent mouillées. L'éclat est là, papa. Tu le vois sur le bord ? Oui, papa. On est bien, ici. La tarte sent le beurre, plus légère. Mes bateaux ont flotté. Jusqu'au bord, Nino. Oui, maman. Nino pose la joue près du bord. Le bord est tiède, un peu. C'est tiède. Tu le sens sur tes joues ? Oui, il est tiède. Une feuille porte une goutte d'eau. Dehors, le jardin s'endort. L'&lt;emphasis&gt;éclat de bassine&lt;/emphasis&gt; tient sur le bord.&lt;/slow&gt;&lt;/soft&gt;&lt;/low-pitch&gt; [long-pause]</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr"/>
@@ -2013,15 +2078,15 @@
         </is>
       </c>
       <c r="Y6" s="2" t="n">
-        <v>136</v>
+        <v>118</v>
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>slow</t>
         </is>
       </c>
       <c r="AA6" s="2" t="n">
-        <v>0.92</v>
+        <v>0.85</v>
       </c>
       <c r="AB6" s="2" t="n">
         <v>1.28</v>
@@ -2033,12 +2098,12 @@
       </c>
       <c r="AD6" s="2" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>-2st</t>
         </is>
       </c>
       <c r="AE6" s="2" t="inlineStr">
         <is>
-          <t>lower-pitch</t>
+          <t>low-pitch</t>
         </is>
       </c>
       <c r="AF6" s="2" t="inlineStr">
@@ -2047,17 +2112,21 @@
         </is>
       </c>
       <c r="AG6" s="2" t="n">
-        <v>-2</v>
-      </c>
-      <c r="AH6" s="2" t="inlineStr"/>
+        <v>-3</v>
+      </c>
+      <c r="AH6" s="2" t="inlineStr">
+        <is>
+          <t>éclat de bassine</t>
+        </is>
+      </c>
       <c r="AI6" s="2" t="n">
         <v>200</v>
       </c>
       <c r="AJ6" s="2" t="n">
-        <v>600</v>
+        <v>900</v>
       </c>
       <c r="AK6" s="2" t="n">
-        <v>280</v>
+        <v>340</v>
       </c>
       <c r="AL6" s="2" t="inlineStr">
         <is>
@@ -2066,11 +2135,11 @@
       </c>
       <c r="AM6" s="2" t="inlineStr">
         <is>
-          <t>fall</t>
+          <t>falling</t>
         </is>
       </c>
       <c r="AN6" s="2" t="n">
-        <v>0.333</v>
+        <v>0.31</v>
       </c>
       <c r="AO6" s="2" t="inlineStr"/>
       <c r="AP6" s="2" t="inlineStr">
@@ -2079,27 +2148,50 @@
         </is>
       </c>
       <c r="AQ6" s="2" t="n">
-        <v>0.92</v>
+        <v>0.85</v>
       </c>
       <c r="AR6" s="2" t="n">
-        <v>0.92</v>
+        <v>0.85</v>
       </c>
       <c r="AS6" s="2" t="n">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="AT6" s="2" t="n">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="AU6" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="AV6" s="2" t="inlineStr"/>
+        <v>12</v>
+      </c>
+      <c r="AV6" s="2" t="inlineStr">
+        <is>
+          <t>arc=retour; intention=refermer; emotion=tendresse et fierté_calme; intensite=1; destinataire=enfant; sous_texte=l_eclat_du_debut_tient_sur_le_bord; tempo=posé; sourire=léger; respiration=ample</t>
+        </is>
+      </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>enfant-m|Les bateaux ont flotté.
-enfant-m|On a joué ensemble.
-maman|Bravo, Nino.
-narrateur|La tarte attend encore un peu.</t>
+          <t>narrateur|Ils restent près de la marche.
+narrateur|Les voiles de feuilles restent mouillées.
+enfant-m|L'éclat est là, papa.
+papa|Tu le vois sur le bord ?
+enfant-m|Oui, papa.
+maman|On est bien, ici.
+narrateur|La tarte sent le beurre, plus légère.
+enfant-m|Mes bateaux ont flotté.
+maman|Jusqu'au bord, Nino.
+enfant-m|Oui, maman.
+narrateur|Nino pose la joue près du bord.
+narrateur|Le bord est tiède, un peu.
+enfant-m|C'est tiède.
+papa|Tu le sens sur tes joues ?
+enfant-m|Oui, il est tiède.
+narrateur|Une feuille porte une goutte d'eau.
+narrateur|Dehors, le jardin s'endort.
+narrateur|L'éclat de bassine tient sur le bord.</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>tarte</t>
         </is>
       </c>
     </row>
@@ -2120,7 +2212,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A11"/>
+  <dimension ref="A1:A12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2198,6 +2290,13 @@
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
         <is>
           <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>
